--- a/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/import-item-result.xlsx
+++ b/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/import-item-result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -27,27 +27,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>仓位代码</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>产品代码</t>
   </si>
   <si>
-    <t>实际库存</t>
+    <t>库位</t>
+  </si>
+  <si>
+    <t>实盘数量</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>库位-16</t>
-  </si>
-  <si>
     <t>ASF0623LEB</t>
   </si>
   <si>
-    <t>DC</t>
+    <t>A-2</t>
   </si>
 </sst>
 </file>
@@ -64,7 +61,7 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -87,7 +84,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -95,7 +92,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -103,14 +100,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -118,7 +115,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,7 +123,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -134,7 +131,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,7 +139,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -150,14 +147,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -165,7 +162,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -173,7 +170,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -181,14 +178,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -196,42 +193,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -719,55 +716,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常規" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
     <cellStyle name="百分比" xfId="3" builtinId="5"/>
     <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
+    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
+    <cellStyle name="註釋" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
+    <cellStyle name="標題" xfId="10" builtinId="15"/>
+    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
+    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
+    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
+    <cellStyle name="輸入" xfId="16" builtinId="20"/>
+    <cellStyle name="輸出" xfId="17" builtinId="21"/>
+    <cellStyle name="計算" xfId="18" builtinId="22"/>
+    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
+    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
+    <cellStyle name="匯總" xfId="21" builtinId="25"/>
     <cellStyle name="好" xfId="22" builtinId="26"/>
     <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="適中" xfId="24" builtinId="28"/>
+    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1251,10 +1248,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="1" max="1" width="15.1818181818182" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" spans="1:4">
@@ -1271,7 +1269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.5" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1279,253 +1277,253 @@
         <v>5</v>
       </c>
       <c r="C2" s="3">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" ht="14.5" spans="1:4">
+    <row r="3" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" ht="14.5" spans="1:4">
+    <row r="4" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" ht="14.5" spans="1:4">
+    <row r="5" spans="1:4">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" ht="14.5" spans="1:4">
+    <row r="6" spans="1:4">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" ht="14.5" spans="1:4">
+    <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" ht="14.5" spans="1:4">
+    <row r="8" spans="1:4">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" ht="14.5" spans="1:4">
+    <row r="9" spans="1:4">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" ht="14.5" spans="1:4">
+    <row r="10" spans="1:4">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" ht="14.5" spans="1:4">
+    <row r="11" spans="1:4">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" ht="14.5" spans="1:4">
+    <row r="12" spans="1:4">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" ht="14.5" spans="1:4">
+    <row r="13" spans="1:4">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" ht="14.5" spans="1:4">
+    <row r="14" spans="1:4">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="14.5" spans="1:4">
+    <row r="15" spans="1:4">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" ht="14.5" spans="1:4">
+    <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" ht="14.5" spans="1:4">
+    <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" ht="14.5" spans="1:4">
+    <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" ht="14.5" spans="1:4">
+    <row r="19" spans="1:4">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" ht="14.5" spans="1:4">
+    <row r="20" spans="1:4">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" ht="14.5" spans="1:4">
+    <row r="21" spans="1:4">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" ht="14.5" spans="1:4">
+    <row r="22" spans="1:4">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" ht="14.5" spans="1:4">
+    <row r="23" spans="1:4">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" ht="14.5" spans="1:4">
+    <row r="24" spans="1:4">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" ht="14.5" spans="1:4">
+    <row r="25" spans="1:4">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" ht="14.5" spans="1:4">
+    <row r="26" spans="1:4">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" ht="14.5" spans="1:4">
+    <row r="27" spans="1:4">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" ht="14.5" spans="1:4">
+    <row r="28" spans="1:4">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" ht="14.5" spans="1:4">
+    <row r="29" spans="1:4">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" ht="14.5" spans="1:4">
+    <row r="30" spans="1:4">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" ht="14.5" spans="1:4">
+    <row r="31" spans="1:4">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" ht="14.5" spans="1:4">
+    <row r="32" spans="1:4">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" ht="14.5" spans="1:4">
+    <row r="33" spans="1:4">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" ht="14.5" spans="1:4">
+    <row r="34" spans="1:4">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" ht="14.5" spans="1:4">
+    <row r="35" spans="1:4">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" ht="14.5" spans="1:4">
+    <row r="36" spans="1:4">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" ht="14.5" spans="1:4">
+    <row r="37" spans="1:4">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" ht="14.5" spans="1:4">
+    <row r="38" spans="1:4">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" ht="14.5" spans="1:4">
+    <row r="39" spans="1:4">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" ht="14.5" spans="1:4">
+    <row r="40" spans="1:4">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" ht="14.5" spans="1:4">
+    <row r="41" spans="1:4">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" ht="14.5" spans="1:4">
+    <row r="42" spans="1:4">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
     </row>
-    <row r="43" ht="14.5" spans="1:4">
+    <row r="43" spans="1:4">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
